--- a/2026/PATXOT 512/Septiembre/PATXOT 521 Septiembre.xlsx
+++ b/2026/PATXOT 512/Septiembre/PATXOT 521 Septiembre.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\2026\PATXOT 512\Agosto\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistemax\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FCC257B-FEBF-4F1E-B19B-74D44FEEC2EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C0BC74F-651F-4ED3-BFAD-77E88113E49A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="detalle y gastos" sheetId="3" r:id="rId1"/>
@@ -18,16 +18,21 @@
     <sheet name="edesur" sheetId="5" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'detalle y gastos'!$A$1:$C$49</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'detalle y gastos'!$A$1:$C$51</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">edesur!$A$1:$H$15</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'prorrateo '!$A$1:$L$16</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'prorrateo '!$A$1:$K$16</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
+  <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="101">
   <si>
     <t>Dpto.</t>
   </si>
@@ -125,18 +130,9 @@
     <t>Inquilinos</t>
   </si>
   <si>
-    <t>CAJA EXTRAORDINARIA</t>
-  </si>
-  <si>
     <t>MP 1148</t>
   </si>
   <si>
-    <t>Pago efectivo</t>
-  </si>
-  <si>
-    <t>Egreso extraordinario</t>
-  </si>
-  <si>
     <t>Egresos por gastos del mes ordinarios</t>
   </si>
   <si>
@@ -276,9 +272,6 @@
   </si>
   <si>
     <t>Honorarios Administracion</t>
-  </si>
-  <si>
-    <t>Poliza de Seguro Obligatoria Mercantil andina N. 1181593</t>
   </si>
   <si>
     <t>Elida</t>
@@ -296,16 +289,55 @@
     <t>Lucia Contartese</t>
   </si>
   <si>
-    <t>Edesur - FEBRERO</t>
-  </si>
-  <si>
     <t>AYSA</t>
   </si>
   <si>
     <t>I Zahar</t>
   </si>
   <si>
-    <t>LIQUIDACIÓN EXPENSAS AGOSTO 2026</t>
+    <t>LIQUIDACIÓN EXPENSAS SEPTIEMBRE 2026</t>
+  </si>
+  <si>
+    <t>Poliza de Seguro Obligatoria Mercantil andina N. 1181593 - Mes de Abril</t>
+  </si>
+  <si>
+    <t>Poliza de Seguro Obligatoria Mercantil andina N. 1181593 - Mes de Mayo</t>
+  </si>
+  <si>
+    <t>Poliza de Seguro Obligatoria Mercantil andina N. 1181593 - Mes de Junio</t>
+  </si>
+  <si>
+    <t>Poliza de Seguro Obligatoria Mercantil andina N. 1181593 - Mes de Julio</t>
+  </si>
+  <si>
+    <t>Poliza de Seguro Obligatoria Mercantil andina N. 1181593 - Mes de Agosto</t>
+  </si>
+  <si>
+    <t>Poliza de Seguro Obligatoria Mercantil andina N. 1181593 - Mes de Septiembre</t>
+  </si>
+  <si>
+    <t>EDESUR ABRIL</t>
+  </si>
+  <si>
+    <t>EDESUR MAYO</t>
+  </si>
+  <si>
+    <t>EDESUR JUNIO</t>
+  </si>
+  <si>
+    <t>EDESUR JULIO</t>
+  </si>
+  <si>
+    <t>EDESUR AGOSTO</t>
+  </si>
+  <si>
+    <t>EDESUR SEPTIEMBRE</t>
+  </si>
+  <si>
+    <t>Se liquidara el mes siguiente</t>
+  </si>
+  <si>
+    <t>Julio Doartero - Cambio de automatico 22/09</t>
   </si>
 </sst>
 </file>
@@ -317,7 +349,7 @@
     <numFmt numFmtId="164" formatCode="_ &quot;$&quot;\ * #,##0.00_ ;_ &quot;$&quot;\ * \-#,##0.00_ ;_ &quot;$&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="165" formatCode="_ &quot;$&quot;\ * #,##0_ ;_ &quot;$&quot;\ * \-#,##0_ ;_ &quot;$&quot;\ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="19" x14ac:knownFonts="1">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -352,14 +384,6 @@
       <b/>
       <u/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -406,30 +430,7 @@
       <family val="2"/>
     </font>
     <font>
-      <b/>
-      <sz val="10"/>
-      <color theme="0"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <color theme="0"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
       <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -954,9 +955,9 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="137">
+  <cellXfs count="124">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -970,52 +971,42 @@
     </xf>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="4" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="8" fillId="4" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="7" fillId="4" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="8" fillId="4" borderId="9" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="7" fillId="4" borderId="9" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="4" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="8" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="4" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="12" fillId="4" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="4" fontId="10" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="4" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="9" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="17" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="8" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="4" fontId="14" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="17" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="7" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="11" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1023,8 +1014,8 @@
     </xf>
     <xf numFmtId="49" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="4" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="4" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1041,21 +1032,21 @@
     <xf numFmtId="44" fontId="0" fillId="8" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="44" fontId="0" fillId="8" borderId="0" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1"/>
@@ -1075,125 +1066,120 @@
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="4" fontId="1" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="5" xfId="2" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="5" xfId="2" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1"/>
-    <xf numFmtId="165" fontId="10" fillId="6" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="9" fillId="6" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="4" fontId="10" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="9" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="4" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="24" xfId="2" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="8" fillId="3" borderId="12" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="8" fillId="3" borderId="27" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="8" fillId="3" borderId="28" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="8" fillId="3" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="8" fillId="3" borderId="11" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="10" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="7" xfId="2" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="24" xfId="2" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="9" fillId="3" borderId="12" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="9" fillId="3" borderId="27" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="9" fillId="3" borderId="28" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="4" fontId="9" fillId="3" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="9" fillId="3" borderId="11" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="4" fontId="14" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -1274,9 +1260,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1314,9 +1300,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1349,9 +1335,26 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1384,9 +1387,26 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1563,411 +1583,423 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:F60"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A2:F54"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="38" customWidth="1"/>
-    <col min="2" max="2" width="40.33203125" customWidth="1"/>
-    <col min="3" max="3" width="16.44140625" customWidth="1"/>
-    <col min="4" max="4" width="12.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="40.28515625" customWidth="1"/>
+    <col min="3" max="3" width="16.42578125" customWidth="1"/>
+    <col min="4" max="4" width="12.140625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
         <v>17</v>
       </c>
       <c r="C2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B4" s="3" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2"/>
-      <c r="B5" s="16"/>
+      <c r="B5" s="14"/>
       <c r="C5" s="2"/>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" s="87" t="s">
-        <v>91</v>
-      </c>
-      <c r="B7" s="17"/>
-      <c r="C7" s="17"/>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="77" t="s">
+        <v>86</v>
+      </c>
+      <c r="B7" s="15"/>
+      <c r="C7" s="15"/>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="8" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A15" s="14" t="s">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" s="12" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A16" s="40" t="s">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" s="31" t="s">
         <v>11</v>
       </c>
-      <c r="B16" s="31"/>
+      <c r="B16" s="27"/>
       <c r="C16" s="6"/>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A17" s="31" t="s">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="27" t="s">
+        <v>84</v>
+      </c>
+      <c r="B17" s="32" t="s">
+        <v>99</v>
+      </c>
+      <c r="C17" s="80">
+        <v>0</v>
+      </c>
+      <c r="D17" s="81"/>
+      <c r="F17" s="7"/>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="33"/>
+      <c r="B18" s="34"/>
+      <c r="C18" s="23">
+        <f>SUM(C17:C17)</f>
+        <v>0</v>
+      </c>
+      <c r="D18" s="24"/>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="31" t="s">
+        <v>18</v>
+      </c>
+      <c r="B19" s="32"/>
+      <c r="C19" s="82"/>
+      <c r="D19" s="24"/>
+    </row>
+    <row r="20" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A20" s="27" t="s">
+        <v>79</v>
+      </c>
+      <c r="B20" s="35"/>
+      <c r="C20" s="29">
+        <v>0</v>
+      </c>
+      <c r="D20" s="24"/>
+      <c r="F20" s="11"/>
+    </row>
+    <row r="21" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A21" s="27" t="s">
+        <v>100</v>
+      </c>
+      <c r="B21" s="35"/>
+      <c r="C21" s="29">
+        <v>110000</v>
+      </c>
+      <c r="D21" s="24"/>
+      <c r="F21" s="11"/>
+    </row>
+    <row r="22" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A22" s="27" t="s">
+        <v>87</v>
+      </c>
+      <c r="B22" s="35"/>
+      <c r="C22" s="29">
+        <v>51187.02</v>
+      </c>
+      <c r="D22" s="24"/>
+      <c r="F22" s="11"/>
+    </row>
+    <row r="23" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A23" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="B23" s="35"/>
+      <c r="C23" s="29">
+        <v>51187.02</v>
+      </c>
+      <c r="D23" s="24"/>
+      <c r="F23" s="11"/>
+    </row>
+    <row r="24" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A24" s="27" t="s">
         <v>89</v>
       </c>
-      <c r="B17" s="41" t="s">
-        <v>34</v>
-      </c>
-      <c r="C17" s="90">
-        <v>232849.09</v>
-      </c>
-      <c r="D17" s="91"/>
-      <c r="F17" s="7"/>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A18" s="42"/>
-      <c r="B18" s="43"/>
-      <c r="C18" s="25">
-        <f>SUM(C17:C17)</f>
-        <v>232849.09</v>
-      </c>
-      <c r="D18" s="26"/>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A19" s="40" t="s">
-        <v>18</v>
-      </c>
-      <c r="B19" s="41"/>
-      <c r="C19" s="92"/>
-      <c r="D19" s="26"/>
-    </row>
-    <row r="20" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A20" s="31" t="s">
-        <v>82</v>
-      </c>
-      <c r="B20" s="44"/>
-      <c r="C20" s="38">
-        <v>37000</v>
-      </c>
-      <c r="D20" s="26"/>
-      <c r="F20" s="13"/>
-    </row>
-    <row r="21" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A21" s="31" t="s">
-        <v>83</v>
-      </c>
-      <c r="B21" s="44"/>
-      <c r="C21" s="136">
+      <c r="B24" s="35"/>
+      <c r="C24" s="29">
         <v>51187.02</v>
       </c>
-      <c r="D21" s="26"/>
-      <c r="F21" s="13"/>
-    </row>
-    <row r="22" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A22" s="31" t="s">
-        <v>81</v>
-      </c>
-      <c r="B22" s="41"/>
-      <c r="C22" s="39"/>
-      <c r="D22" s="93"/>
-      <c r="E22" s="7"/>
-      <c r="F22" s="13"/>
-    </row>
-    <row r="23" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A23" s="42"/>
-      <c r="B23" s="43"/>
-      <c r="C23" s="25">
-        <f>SUM(C19:C22)</f>
-        <v>88187.01999999999</v>
-      </c>
-      <c r="F23" s="13"/>
-    </row>
-    <row r="24" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A24" s="35" t="s">
-        <v>47</v>
-      </c>
-      <c r="B24" s="35"/>
-      <c r="C24" s="45">
-        <f>+C23+C18</f>
-        <v>321036.11</v>
-      </c>
-      <c r="F24" s="13"/>
-    </row>
-    <row r="25" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="C25" s="26"/>
-      <c r="F25" s="13"/>
-    </row>
-    <row r="26" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A26" s="14" t="s">
+      <c r="D24" s="24"/>
+      <c r="F24" s="11"/>
+    </row>
+    <row r="25" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A25" s="27" t="s">
+        <v>90</v>
+      </c>
+      <c r="B25" s="35"/>
+      <c r="C25" s="29">
+        <v>51187.02</v>
+      </c>
+      <c r="D25" s="24"/>
+      <c r="F25" s="11"/>
+    </row>
+    <row r="26" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A26" s="27" t="s">
+        <v>91</v>
+      </c>
+      <c r="B26" s="35"/>
+      <c r="C26" s="29">
+        <v>51187.02</v>
+      </c>
+      <c r="D26" s="24"/>
+      <c r="F26" s="11"/>
+    </row>
+    <row r="27" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A27" s="27" t="s">
+        <v>92</v>
+      </c>
+      <c r="B27" s="35"/>
+      <c r="C27" s="29">
+        <v>51187.02</v>
+      </c>
+      <c r="D27" s="24"/>
+      <c r="F27" s="11"/>
+    </row>
+    <row r="28" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A28" s="27" t="s">
+        <v>93</v>
+      </c>
+      <c r="B28" s="35"/>
+      <c r="C28" s="29">
+        <v>137401.09</v>
+      </c>
+      <c r="D28" s="24"/>
+      <c r="F28" s="11"/>
+    </row>
+    <row r="29" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A29" s="27" t="s">
+        <v>94</v>
+      </c>
+      <c r="B29" s="35"/>
+      <c r="C29" s="29">
+        <v>163668.04</v>
+      </c>
+      <c r="D29" s="25"/>
+      <c r="F29" s="11"/>
+    </row>
+    <row r="30" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A30" s="27" t="s">
+        <v>95</v>
+      </c>
+      <c r="B30" s="35"/>
+      <c r="C30" s="29">
+        <v>177511.73</v>
+      </c>
+      <c r="D30" s="24"/>
+      <c r="F30" s="11"/>
+    </row>
+    <row r="31" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A31" s="27" t="s">
+        <v>96</v>
+      </c>
+      <c r="B31" s="35"/>
+      <c r="C31" s="29">
+        <v>176229</v>
+      </c>
+      <c r="D31" s="24"/>
+      <c r="F31" s="11"/>
+    </row>
+    <row r="32" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A32" s="27" t="s">
+        <v>97</v>
+      </c>
+      <c r="B32" s="35"/>
+      <c r="C32" s="29">
+        <v>204540.77</v>
+      </c>
+      <c r="D32" s="24"/>
+      <c r="F32" s="11"/>
+    </row>
+    <row r="33" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A33" s="27" t="s">
+        <v>98</v>
+      </c>
+      <c r="B33" s="35"/>
+      <c r="C33" s="29">
+        <v>212900.33</v>
+      </c>
+      <c r="D33" s="24"/>
+      <c r="F33" s="11"/>
+    </row>
+    <row r="34" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A34" s="27" t="s">
+        <v>78</v>
+      </c>
+      <c r="B34" s="32"/>
+      <c r="C34" s="30"/>
+      <c r="D34" s="83"/>
+      <c r="E34" s="7"/>
+      <c r="F34" s="11"/>
+    </row>
+    <row r="35" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A35" s="33"/>
+      <c r="B35" s="34"/>
+      <c r="C35" s="23">
+        <f>SUM(C19:C34)</f>
+        <v>1489373.08</v>
+      </c>
+      <c r="F35" s="11"/>
+    </row>
+    <row r="36" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A36" s="28" t="s">
+        <v>44</v>
+      </c>
+      <c r="B36" s="28"/>
+      <c r="C36" s="36">
+        <f>+C35+C18</f>
+        <v>1489373.08</v>
+      </c>
+      <c r="F36" s="11"/>
+    </row>
+    <row r="37" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="C37" s="24"/>
+      <c r="F37" s="11"/>
+    </row>
+    <row r="38" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A38" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="C26" s="26"/>
-      <c r="F26" s="13"/>
-    </row>
-    <row r="27" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A27" s="31"/>
-      <c r="B27" s="31"/>
-      <c r="C27" s="38"/>
-      <c r="F27" s="13"/>
-    </row>
-    <row r="28" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A28" s="31"/>
-      <c r="B28" s="31"/>
-      <c r="C28" s="39"/>
-      <c r="F28" s="13"/>
-    </row>
-    <row r="29" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A29" s="31"/>
-      <c r="B29" s="31"/>
-      <c r="C29" s="39"/>
-      <c r="F29" s="13"/>
-    </row>
-    <row r="30" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="C30" s="27"/>
-      <c r="F30" s="13"/>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A31" s="14" t="s">
+      <c r="C38" s="24"/>
+      <c r="F38" s="11"/>
+    </row>
+    <row r="39" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A39" s="27"/>
+      <c r="B39" s="27"/>
+      <c r="C39" s="29"/>
+      <c r="F39" s="11"/>
+    </row>
+    <row r="40" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A40" s="27"/>
+      <c r="B40" s="27"/>
+      <c r="C40" s="30"/>
+      <c r="F40" s="11"/>
+    </row>
+    <row r="41" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A41" s="27"/>
+      <c r="B41" s="27"/>
+      <c r="C41" s="30"/>
+      <c r="F41" s="11"/>
+    </row>
+    <row r="42" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="C42" s="25"/>
+      <c r="F42" s="11"/>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A43" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="B31" s="14"/>
-      <c r="C31" s="15">
-        <f>+C27+C28+C29+C30</f>
+      <c r="B43" s="12"/>
+      <c r="C43" s="13">
+        <f>+C39+C40+C41+C42</f>
         <v>0</v>
       </c>
-      <c r="E31" s="7"/>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A33" s="20" t="s">
+      <c r="E43" s="7"/>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A45" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="B33" s="20"/>
-      <c r="C33" s="21">
-        <f>+C31+C24</f>
-        <v>321036.11</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="35" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A35" s="83" t="s">
+      <c r="B45" s="18"/>
+      <c r="C45" s="19">
+        <f>+C43+C36</f>
+        <v>1489373.08</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="47" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="73" t="s">
         <v>19</v>
       </c>
-      <c r="B35" s="84"/>
-      <c r="C35" s="85"/>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A36" s="81" t="s">
+      <c r="B47" s="74"/>
+      <c r="C47" s="75"/>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A48" s="71" t="s">
         <v>8</v>
       </c>
-      <c r="B36" s="2"/>
-      <c r="C36" s="82">
-        <v>-542364.40844549204</v>
-      </c>
-      <c r="D36" s="5"/>
-      <c r="E36" s="5"/>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A37" t="s">
+      <c r="B48" s="2"/>
+      <c r="C48" s="72">
+        <v>-827188.07844549208</v>
+      </c>
+      <c r="D48" s="5"/>
+      <c r="E48" s="5"/>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
         <v>7</v>
       </c>
-      <c r="C37" s="18">
+      <c r="C49" s="16">
         <f>'prorrateo '!F15</f>
-        <v>173513.09999999998</v>
-      </c>
-      <c r="D37" s="7"/>
-      <c r="E37" s="7"/>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A38" t="s">
-        <v>88</v>
-      </c>
-      <c r="C38" s="46">
-        <f>-edesur!H1</f>
-        <v>-137300.66000000003</v>
-      </c>
-      <c r="D38" s="7"/>
-      <c r="E38" s="7"/>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A39" t="s">
-        <v>36</v>
-      </c>
-      <c r="C39" s="46">
-        <f>-C24</f>
-        <v>-321036.11</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A40" s="22" t="s">
+        <v>304433.89977409336</v>
+      </c>
+      <c r="D49" s="7"/>
+      <c r="E49" s="7"/>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>33</v>
+      </c>
+      <c r="C50" s="37">
+        <f>-C36</f>
+        <v>-1489373.08</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A51" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="B40" s="19"/>
-      <c r="C40" s="23">
-        <f>SUM(C36:C39)</f>
-        <v>-827188.07844549208</v>
-      </c>
-      <c r="D40" s="5"/>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A41" s="10"/>
-      <c r="B41" s="9"/>
-      <c r="C41" s="11"/>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A42" s="119" t="str">
-        <f>'prorrateo '!A16:L16</f>
-        <v>Atención: se han reliquidado todas las deudas correspondientes a cada unidad funcional, dejando reflejados los saldos reales de cada una.
-A partir de este mes se aplicarán intereses a quienes no abonen las expensas en tiempo y forma.
-La columna Ingresos registra pagos efectuados tanto durante el mes de enero como en meses anteriores. Por este motivo, en la caja general se han descontado aquellos pagos que no corresponden al período liquidado, a fin de evitar su doble contabilización, ya que los mismos fueron imputados oportunamente en expensas anteriores.
-Del mismo modo, los saldos anteriores incluyen montos correspondientes a expensas adeudadas no solo del mes de diciembre, sino también de meses posteriores.</v>
-      </c>
-      <c r="B42" s="119"/>
-      <c r="C42" s="119"/>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A43" s="119"/>
-      <c r="B43" s="119"/>
-      <c r="C43" s="119"/>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A44" s="119"/>
-      <c r="B44" s="119"/>
-      <c r="C44" s="119"/>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A45" s="119"/>
-      <c r="B45" s="119"/>
-      <c r="C45" s="119"/>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A46" s="119"/>
-      <c r="B46" s="119"/>
-      <c r="C46" s="119"/>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A47" s="119"/>
-      <c r="B47" s="119"/>
-      <c r="C47" s="119"/>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A48" s="119"/>
-      <c r="B48" s="119"/>
-      <c r="C48" s="119"/>
-    </row>
-    <row r="49" spans="1:6" ht="81.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="119"/>
-      <c r="B49" s="119"/>
-      <c r="C49" s="119"/>
-    </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A50" s="10"/>
-      <c r="B50" s="9"/>
-      <c r="C50" s="11"/>
-      <c r="F50" s="47"/>
-    </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A51" s="10"/>
-      <c r="B51" s="9"/>
-      <c r="C51" s="11"/>
-    </row>
-    <row r="52" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A52" s="29" t="s">
-        <v>32</v>
-      </c>
-      <c r="B52" s="30"/>
-      <c r="C52" s="33">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A53" s="31" t="s">
-        <v>35</v>
-      </c>
-      <c r="B53" s="31"/>
-      <c r="C53" s="36">
-        <f>-C31</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A54" s="31"/>
-      <c r="B54" s="31"/>
-      <c r="C54" s="36"/>
-    </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A55" s="31"/>
-      <c r="B55" s="31"/>
-      <c r="C55" s="37"/>
-    </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A56" s="35" t="s">
-        <v>3</v>
-      </c>
-      <c r="B56" s="32"/>
-      <c r="C56" s="34">
-        <f>SUM(C52:C55)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A57" s="9"/>
-      <c r="B57" s="9"/>
-      <c r="C57" s="9"/>
-    </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A58" s="9"/>
-      <c r="B58" s="9"/>
-      <c r="C58" s="9"/>
-    </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A59" s="9"/>
-      <c r="B59" s="9"/>
-      <c r="C59" s="9"/>
-    </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A60" s="9"/>
-      <c r="B60" s="9"/>
-      <c r="C60" s="9"/>
+      <c r="B51" s="17"/>
+      <c r="C51" s="21">
+        <f>SUM(C48:C50)</f>
+        <v>-2012127.2586713987</v>
+      </c>
+      <c r="D51" s="5"/>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A52" s="9"/>
+      <c r="B52" s="9"/>
+      <c r="C52" s="9"/>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A53" s="9"/>
+      <c r="B53" s="9"/>
+      <c r="C53" s="9"/>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A54" s="9"/>
+      <c r="B54" s="9"/>
+      <c r="C54" s="9"/>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A42:C49"/>
-  </mergeCells>
   <hyperlinks>
     <hyperlink ref="B4" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
   </hyperlinks>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.19685039370078741" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
-  <pageSetup paperSize="9" scale="97" orientation="portrait" r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId2"/>
   <drawing r:id="rId3"/>
 </worksheet>
 </file>
@@ -1977,557 +2009,530 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:N16"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:M16"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.33203125" style="1" customWidth="1"/>
+    <col min="1" max="1" width="5.28515625" style="1" customWidth="1"/>
     <col min="2" max="2" width="4" style="1" customWidth="1"/>
-    <col min="3" max="3" width="23.44140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.88671875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.6640625" customWidth="1"/>
-    <col min="6" max="6" width="10.6640625" customWidth="1"/>
-    <col min="7" max="7" width="12.21875" customWidth="1"/>
-    <col min="8" max="8" width="10.33203125" customWidth="1"/>
-    <col min="9" max="9" width="8.33203125" customWidth="1"/>
-    <col min="10" max="10" width="13.109375" customWidth="1"/>
-    <col min="11" max="11" width="11.44140625" customWidth="1"/>
-    <col min="12" max="12" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="11.44140625" style="12"/>
+    <col min="3" max="3" width="23.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.5703125" customWidth="1"/>
+    <col min="5" max="5" width="11.7109375" customWidth="1"/>
+    <col min="6" max="6" width="10.7109375" customWidth="1"/>
+    <col min="7" max="7" width="12.28515625" customWidth="1"/>
+    <col min="8" max="8" width="10.28515625" customWidth="1"/>
+    <col min="9" max="9" width="8.28515625" customWidth="1"/>
+    <col min="10" max="10" width="13.5703125" customWidth="1"/>
+    <col min="11" max="11" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="11.42578125" style="10"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="95" t="s">
+    <row r="1" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="85" t="s">
         <v>29</v>
       </c>
-      <c r="B1" s="96"/>
-      <c r="C1" s="26"/>
-      <c r="D1" s="26"/>
-      <c r="E1" s="27">
-        <v>321036.11</v>
-      </c>
-      <c r="F1" s="26"/>
-      <c r="G1" s="26"/>
-      <c r="H1" s="126"/>
-      <c r="I1" s="126"/>
-      <c r="J1" s="27"/>
-      <c r="K1" s="26"/>
-      <c r="L1" s="26"/>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A2" s="97">
+      <c r="B1" s="86"/>
+      <c r="C1" s="24"/>
+      <c r="D1" s="24"/>
+      <c r="E1" s="25">
+        <v>1489373.08</v>
+      </c>
+      <c r="F1" s="24"/>
+      <c r="G1" s="24"/>
+      <c r="H1" s="112"/>
+      <c r="I1" s="112"/>
+      <c r="J1" s="25"/>
+      <c r="K1" s="24"/>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2" s="87">
         <f>'detalle y gastos'!B7</f>
         <v>0</v>
       </c>
-      <c r="B2" s="98"/>
-      <c r="C2" s="99"/>
-      <c r="D2" s="99"/>
-      <c r="E2" s="100"/>
-      <c r="F2" s="98"/>
-      <c r="G2" s="98"/>
-      <c r="H2" s="98"/>
-      <c r="I2" s="98"/>
-      <c r="J2" s="101"/>
-      <c r="K2" s="101"/>
-      <c r="L2" s="102"/>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A3" s="132" t="s">
+      <c r="B2" s="88"/>
+      <c r="C2" s="89"/>
+      <c r="D2" s="89"/>
+      <c r="E2" s="90"/>
+      <c r="F2" s="88"/>
+      <c r="G2" s="88"/>
+      <c r="H2" s="88"/>
+      <c r="I2" s="88"/>
+      <c r="J2" s="91"/>
+      <c r="K2" s="92"/>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A3" s="120" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="133"/>
-      <c r="C3" s="120" t="s">
+      <c r="B3" s="121"/>
+      <c r="C3" s="116" t="s">
         <v>1</v>
       </c>
-      <c r="D3" s="130" t="s">
+      <c r="D3" s="118" t="s">
         <v>31</v>
       </c>
-      <c r="E3" s="103" t="s">
+      <c r="E3" s="93" t="s">
         <v>15</v>
       </c>
-      <c r="F3" s="103" t="s">
+      <c r="F3" s="93" t="s">
         <v>2</v>
       </c>
-      <c r="G3" s="120" t="s">
+      <c r="G3" s="116" t="s">
         <v>30</v>
       </c>
-      <c r="H3" s="120" t="s">
+      <c r="H3" s="116" t="s">
         <v>26</v>
       </c>
-      <c r="I3" s="128" t="s">
+      <c r="I3" s="114" t="s">
         <v>5</v>
       </c>
-      <c r="J3" s="122" t="s">
-        <v>79</v>
-      </c>
-      <c r="K3" s="120" t="s">
-        <v>24</v>
-      </c>
-      <c r="L3" s="104" t="s">
+      <c r="J3" s="108" t="s">
+        <v>76</v>
+      </c>
+      <c r="K3" s="94" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A4" s="134"/>
-      <c r="B4" s="135"/>
-      <c r="C4" s="121"/>
-      <c r="D4" s="131"/>
-      <c r="E4" s="105" t="s">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A4" s="122"/>
+      <c r="B4" s="123"/>
+      <c r="C4" s="117"/>
+      <c r="D4" s="119"/>
+      <c r="E4" s="95" t="s">
         <v>16</v>
       </c>
-      <c r="F4" s="103" t="s">
+      <c r="F4" s="93" t="s">
         <v>27</v>
       </c>
-      <c r="G4" s="121"/>
-      <c r="H4" s="121"/>
-      <c r="I4" s="129"/>
-      <c r="J4" s="123"/>
-      <c r="K4" s="121"/>
-      <c r="L4" s="106" t="s">
+      <c r="G4" s="117"/>
+      <c r="H4" s="117"/>
+      <c r="I4" s="115"/>
+      <c r="J4" s="109"/>
+      <c r="K4" s="96" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:13" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="124">
+    <row r="5" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="110">
         <v>1</v>
       </c>
-      <c r="B5" s="125"/>
-      <c r="C5" s="48" t="s">
+      <c r="B5" s="111"/>
+      <c r="C5" s="38" t="s">
+        <v>34</v>
+      </c>
+      <c r="D5" s="22"/>
+      <c r="E5" s="76">
+        <v>100131.19854098887</v>
+      </c>
+      <c r="F5" s="76">
+        <f>E5</f>
+        <v>100131.19854098887</v>
+      </c>
+      <c r="G5" s="97">
+        <f>E5-F5</f>
+        <v>0</v>
+      </c>
+      <c r="H5" s="97">
+        <f>IF(G5&gt;0,G5*6%,0)</f>
+        <v>0</v>
+      </c>
+      <c r="I5" s="30">
+        <v>13.8</v>
+      </c>
+      <c r="J5" s="98">
+        <f>E$1*I5/100</f>
+        <v>205533.48504</v>
+      </c>
+      <c r="K5" s="99">
+        <f>G5+H5+J5</f>
+        <v>205533.48504</v>
+      </c>
+      <c r="L5" s="79"/>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A6" s="110">
+        <v>2</v>
+      </c>
+      <c r="B6" s="111"/>
+      <c r="C6" s="38" t="s">
+        <v>35</v>
+      </c>
+      <c r="D6" s="26" t="s">
+        <v>85</v>
+      </c>
+      <c r="E6" s="76">
+        <v>348047.31889063603</v>
+      </c>
+      <c r="F6" s="76">
+        <v>0</v>
+      </c>
+      <c r="G6" s="97">
+        <f t="shared" ref="G6:G14" si="0">E6-F6</f>
+        <v>348047.31889063603</v>
+      </c>
+      <c r="H6" s="97">
+        <f t="shared" ref="H6:H14" si="1">IF(G6&gt;0,G6*6%,0)</f>
+        <v>20882.839133438159</v>
+      </c>
+      <c r="I6" s="30">
+        <v>11.86</v>
+      </c>
+      <c r="J6" s="98">
+        <f t="shared" ref="J6:J14" si="2">E$1*I6/100</f>
+        <v>176639.64728799998</v>
+      </c>
+      <c r="K6" s="99">
+        <f t="shared" ref="K6:K14" si="3">G6+H6+J6</f>
+        <v>545569.80531207414</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A7" s="110">
+        <v>3</v>
+      </c>
+      <c r="B7" s="111"/>
+      <c r="C7" s="38" t="s">
+        <v>35</v>
+      </c>
+      <c r="D7" s="26" t="s">
+        <v>39</v>
+      </c>
+      <c r="E7" s="76">
+        <v>289720.20084672421</v>
+      </c>
+      <c r="F7" s="76">
+        <v>0</v>
+      </c>
+      <c r="G7" s="97">
+        <f t="shared" si="0"/>
+        <v>289720.20084672421</v>
+      </c>
+      <c r="H7" s="97">
+        <f t="shared" si="1"/>
+        <v>17383.212050803453</v>
+      </c>
+      <c r="I7" s="30">
+        <v>12.46</v>
+      </c>
+      <c r="J7" s="98">
+        <f t="shared" si="2"/>
+        <v>185575.88576800004</v>
+      </c>
+      <c r="K7" s="99">
+        <f t="shared" si="3"/>
+        <v>492679.29866552772</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A8" s="110">
+        <v>4</v>
+      </c>
+      <c r="B8" s="111"/>
+      <c r="C8" s="38" t="s">
+        <v>36</v>
+      </c>
+      <c r="D8" s="26" t="s">
+        <v>80</v>
+      </c>
+      <c r="E8" s="76">
+        <v>102716.87833037041</v>
+      </c>
+      <c r="F8" s="76">
+        <v>0</v>
+      </c>
+      <c r="G8" s="97">
+        <f t="shared" si="0"/>
+        <v>102716.87833037041</v>
+      </c>
+      <c r="H8" s="97">
+        <f t="shared" si="1"/>
+        <v>6163.012699822224</v>
+      </c>
+      <c r="I8" s="30">
+        <v>14.75</v>
+      </c>
+      <c r="J8" s="98">
+        <f t="shared" si="2"/>
+        <v>219682.52929999999</v>
+      </c>
+      <c r="K8" s="99">
+        <f t="shared" si="3"/>
+        <v>328562.42033019266</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="110">
+        <v>5</v>
+      </c>
+      <c r="B9" s="111"/>
+      <c r="C9" s="38" t="s">
         <v>37</v>
       </c>
-      <c r="D5" s="24"/>
-      <c r="E5" s="86">
-        <v>43247.842278805976</v>
-      </c>
-      <c r="F5" s="86"/>
-      <c r="G5" s="107">
-        <f>E5-F5</f>
-        <v>43247.842278805976</v>
-      </c>
-      <c r="H5" s="107">
-        <f>IF(G5&gt;0,G5*6%,0)</f>
-        <v>2594.8705367283583</v>
-      </c>
-      <c r="I5" s="39">
-        <v>13.8</v>
-      </c>
-      <c r="J5" s="108">
-        <f>E$1*I5/100</f>
-        <v>44302.983180000003</v>
-      </c>
-      <c r="K5" s="109">
-        <f>edesur!H5</f>
-        <v>9985.5025454545466</v>
-      </c>
-      <c r="L5" s="110">
-        <f>G5+H5+J5+K5</f>
-        <v>100131.19854098887</v>
-      </c>
-      <c r="M5" s="89"/>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A6" s="124">
-        <v>2</v>
-      </c>
-      <c r="B6" s="125"/>
-      <c r="C6" s="48" t="s">
+      <c r="D9" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="E9" s="76">
+        <v>73984.069211120441</v>
+      </c>
+      <c r="F9" s="76">
+        <f>E9</f>
+        <v>73984.069211120441</v>
+      </c>
+      <c r="G9" s="97">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H9" s="97">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I9" s="30">
+        <v>12.41</v>
+      </c>
+      <c r="J9" s="98">
+        <f t="shared" si="2"/>
+        <v>184831.19922800001</v>
+      </c>
+      <c r="K9" s="99">
+        <f t="shared" si="3"/>
+        <v>184831.19922800001</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="110">
+        <v>6</v>
+      </c>
+      <c r="B10" s="111"/>
+      <c r="C10" s="38" t="s">
         <v>38</v>
       </c>
-      <c r="D6" s="28" t="s">
-        <v>90</v>
-      </c>
-      <c r="E6" s="86">
-        <v>246267.42808670638</v>
-      </c>
-      <c r="F6" s="86"/>
-      <c r="G6" s="107">
-        <f t="shared" ref="G6:G14" si="0">E6-F6</f>
-        <v>246267.42808670638</v>
-      </c>
-      <c r="H6" s="107">
-        <f t="shared" ref="H6:H14" si="1">IF(G6&gt;0,G6*6%,0)</f>
-        <v>14776.045685202382</v>
-      </c>
-      <c r="I6" s="39">
-        <v>11.86</v>
-      </c>
-      <c r="J6" s="108">
-        <f t="shared" ref="J6:J14" si="2">E$1*I6/100</f>
-        <v>38074.882645999998</v>
-      </c>
-      <c r="K6" s="109">
-        <f>edesur!H6</f>
-        <v>48928.962472727282</v>
-      </c>
-      <c r="L6" s="110">
-        <f t="shared" ref="L6:L14" si="3">G6+H6+J6+K6</f>
-        <v>348047.31889063603</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" ht="27" x14ac:dyDescent="0.3">
-      <c r="A7" s="124">
-        <v>3</v>
-      </c>
-      <c r="B7" s="125"/>
-      <c r="C7" s="48" t="s">
-        <v>38</v>
-      </c>
-      <c r="D7" s="28" t="s">
-        <v>42</v>
-      </c>
-      <c r="E7" s="86">
-        <v>189895.67376912234</v>
-      </c>
-      <c r="F7" s="86"/>
-      <c r="G7" s="107">
+      <c r="D10" s="26"/>
+      <c r="E10" s="76">
+        <v>277039.7847910584</v>
+      </c>
+      <c r="F10" s="76">
+        <v>0</v>
+      </c>
+      <c r="G10" s="97">
         <f t="shared" si="0"/>
-        <v>189895.67376912234</v>
-      </c>
-      <c r="H7" s="107">
+        <v>277039.7847910584</v>
+      </c>
+      <c r="H10" s="97">
         <f t="shared" si="1"/>
-        <v>11393.74042614734</v>
-      </c>
-      <c r="I7" s="39">
-        <v>12.46</v>
-      </c>
-      <c r="J7" s="108">
+        <v>16622.387087463503</v>
+      </c>
+      <c r="I10" s="30">
+        <v>12.48</v>
+      </c>
+      <c r="J10" s="98">
         <f t="shared" si="2"/>
-        <v>40001.099306000004</v>
-      </c>
-      <c r="K7" s="109">
-        <f>edesur!H7</f>
-        <v>48429.687345454557</v>
-      </c>
-      <c r="L7" s="110">
+        <v>185873.76038400002</v>
+      </c>
+      <c r="K10" s="99">
         <f t="shared" si="3"/>
-        <v>289720.20084672421</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A8" s="124">
-        <v>4</v>
-      </c>
-      <c r="B8" s="125"/>
-      <c r="C8" s="48" t="s">
-        <v>39</v>
-      </c>
-      <c r="D8" s="28" t="s">
-        <v>84</v>
-      </c>
-      <c r="E8" s="86">
-        <v>172809.95241501497</v>
-      </c>
-      <c r="F8" s="86">
-        <v>130000</v>
-      </c>
-      <c r="G8" s="107">
+        <v>479535.93226252194</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="110">
+        <v>7</v>
+      </c>
+      <c r="B11" s="111"/>
+      <c r="C11" s="26" t="s">
+        <v>83</v>
+      </c>
+      <c r="D11" s="26"/>
+      <c r="E11" s="76">
+        <v>125759.03756706888</v>
+      </c>
+      <c r="F11" s="76">
+        <v>122525</v>
+      </c>
+      <c r="G11" s="97">
         <f t="shared" si="0"/>
-        <v>42809.952415014966</v>
-      </c>
-      <c r="H8" s="107">
+        <v>3234.0375670688809</v>
+      </c>
+      <c r="H11" s="97">
         <f t="shared" si="1"/>
-        <v>2568.597144900898</v>
-      </c>
-      <c r="I8" s="39">
-        <v>14.75</v>
-      </c>
-      <c r="J8" s="108">
+        <v>194.04225402413286</v>
+      </c>
+      <c r="I11" s="30">
+        <v>18.260000000000002</v>
+      </c>
+      <c r="J11" s="98">
         <f t="shared" si="2"/>
-        <v>47352.826224999997</v>
-      </c>
-      <c r="K8" s="109">
-        <f>edesur!H8</f>
-        <v>9985.5025454545466</v>
-      </c>
-      <c r="L8" s="110">
+        <v>271959.52440800006</v>
+      </c>
+      <c r="K11" s="99">
         <f t="shared" si="3"/>
-        <v>102716.87833037041</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="124">
-        <v>5</v>
-      </c>
-      <c r="B9" s="125"/>
-      <c r="C9" s="48" t="s">
-        <v>40</v>
-      </c>
-      <c r="D9" s="28" t="s">
-        <v>43</v>
-      </c>
-      <c r="E9" s="86">
-        <v>74259.887698226841</v>
-      </c>
-      <c r="F9" s="86">
-        <v>42049.05</v>
-      </c>
-      <c r="G9" s="107">
-        <f t="shared" si="0"/>
-        <v>32210.837698226838</v>
-      </c>
-      <c r="H9" s="107">
-        <f t="shared" si="1"/>
-        <v>1932.6502618936101</v>
-      </c>
-      <c r="I9" s="39">
-        <v>12.41</v>
-      </c>
-      <c r="J9" s="108">
-        <f t="shared" si="2"/>
-        <v>39840.581250999996</v>
-      </c>
-      <c r="K9" s="109">
-        <f>edesur!H9</f>
-        <v>0</v>
-      </c>
-      <c r="L9" s="110">
-        <f>G9+H9+J9+K9</f>
-        <v>73984.069211120441</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="124">
-        <v>6</v>
-      </c>
-      <c r="B10" s="125"/>
-      <c r="C10" s="48" t="s">
+        <v>275387.60422909306</v>
+      </c>
+      <c r="L11" s="79"/>
+    </row>
+    <row r="12" spans="1:12" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="110" t="s">
         <v>41</v>
       </c>
-      <c r="D10" s="28"/>
-      <c r="E10" s="86">
-        <v>214140.54312981496</v>
-      </c>
-      <c r="F10" s="86"/>
-      <c r="G10" s="107">
-        <f t="shared" si="0"/>
-        <v>214140.54312981496</v>
-      </c>
-      <c r="H10" s="107">
-        <f t="shared" si="1"/>
-        <v>12848.432587788897</v>
-      </c>
-      <c r="I10" s="39">
-        <v>12.48</v>
-      </c>
-      <c r="J10" s="108">
-        <f t="shared" si="2"/>
-        <v>40065.306528000001</v>
-      </c>
-      <c r="K10" s="109">
-        <f>edesur!H10</f>
-        <v>9985.5025454545466</v>
-      </c>
-      <c r="L10" s="110">
-        <f t="shared" si="3"/>
-        <v>277039.7847910584</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="124">
-        <v>7</v>
-      </c>
-      <c r="B11" s="125"/>
-      <c r="C11" s="28" t="s">
-        <v>87</v>
-      </c>
-      <c r="D11" s="28"/>
-      <c r="E11" s="86">
-        <v>53917.303146805978</v>
-      </c>
-      <c r="F11" s="86"/>
-      <c r="G11" s="107">
-        <f t="shared" si="0"/>
-        <v>53917.303146805978</v>
-      </c>
-      <c r="H11" s="107">
-        <f t="shared" si="1"/>
-        <v>3235.0381888083584</v>
-      </c>
-      <c r="I11" s="39">
-        <v>18.260000000000002</v>
-      </c>
-      <c r="J11" s="108">
-        <f t="shared" si="2"/>
-        <v>58621.193686000006</v>
-      </c>
-      <c r="K11" s="109">
-        <f>edesur!H11</f>
-        <v>9985.5025454545466</v>
-      </c>
-      <c r="L11" s="110">
-        <f t="shared" si="3"/>
-        <v>125759.03756706888</v>
-      </c>
-      <c r="M11" s="89"/>
-    </row>
-    <row r="12" spans="1:13" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="124" t="s">
-        <v>44</v>
-      </c>
-      <c r="B12" s="125"/>
-      <c r="C12" s="48" t="str">
+      <c r="B12" s="111"/>
+      <c r="C12" s="38" t="str">
         <f>C9</f>
         <v>Grand Jorge</v>
       </c>
-      <c r="D12" s="88" t="s">
-        <v>43</v>
-      </c>
-      <c r="E12" s="86">
-        <v>4758.1520264000019</v>
-      </c>
-      <c r="F12" s="86">
-        <v>1464.05</v>
-      </c>
-      <c r="G12" s="107">
+      <c r="D12" s="78" t="s">
+        <v>40</v>
+      </c>
+      <c r="E12" s="76">
+        <v>7793.6320219840018</v>
+      </c>
+      <c r="F12" s="76">
+        <f>E12</f>
+        <v>7793.6320219840018</v>
+      </c>
+      <c r="G12" s="97">
         <f t="shared" si="0"/>
-        <v>3294.1020264000017</v>
-      </c>
-      <c r="H12" s="107">
+        <v>0</v>
+      </c>
+      <c r="H12" s="97">
         <f t="shared" si="1"/>
-        <v>197.6461215840001</v>
-      </c>
-      <c r="I12" s="39">
+        <v>0</v>
+      </c>
+      <c r="I12" s="30">
         <v>1.34</v>
       </c>
-      <c r="J12" s="108">
+      <c r="J12" s="98">
         <f t="shared" si="2"/>
-        <v>4301.8838740000001</v>
-      </c>
-      <c r="K12" s="109"/>
-      <c r="L12" s="110">
+        <v>19957.599272000003</v>
+      </c>
+      <c r="K12" s="99">
         <f t="shared" si="3"/>
-        <v>7793.6320219840018</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A13" s="124" t="s">
-        <v>45</v>
-      </c>
-      <c r="B13" s="125"/>
-      <c r="C13" s="48" t="str">
+        <v>19957.599272000003</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A13" s="110" t="s">
+        <v>42</v>
+      </c>
+      <c r="B13" s="111"/>
+      <c r="C13" s="38" t="str">
         <f>C6</f>
         <v>Maceyle Gabriela</v>
       </c>
-      <c r="D13" s="28"/>
-      <c r="E13" s="86">
-        <v>51233.939347200001</v>
-      </c>
-      <c r="F13" s="86"/>
-      <c r="G13" s="107">
+      <c r="D13" s="26"/>
+      <c r="E13" s="76">
+        <v>58545.652360032</v>
+      </c>
+      <c r="F13" s="76">
+        <v>0</v>
+      </c>
+      <c r="G13" s="97">
         <f t="shared" si="0"/>
-        <v>51233.939347200001</v>
-      </c>
-      <c r="H13" s="107">
+        <v>58545.652360032</v>
+      </c>
+      <c r="H13" s="97">
         <f t="shared" si="1"/>
-        <v>3074.0363608319999</v>
-      </c>
-      <c r="I13" s="39">
+        <v>3512.73914160192</v>
+      </c>
+      <c r="I13" s="30">
         <v>1.32</v>
       </c>
-      <c r="J13" s="108">
+      <c r="J13" s="98">
         <f t="shared" si="2"/>
-        <v>4237.6766520000001</v>
-      </c>
-      <c r="K13" s="109"/>
-      <c r="L13" s="110">
+        <v>19659.724656000002</v>
+      </c>
+      <c r="K13" s="99">
         <f t="shared" si="3"/>
-        <v>58545.652360032</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="124" t="s">
-        <v>46</v>
-      </c>
-      <c r="B14" s="125"/>
-      <c r="C14" s="24" t="str">
+        <v>81718.116157633922</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="110" t="s">
+        <v>43</v>
+      </c>
+      <c r="B14" s="111"/>
+      <c r="C14" s="22" t="str">
         <f>C6</f>
         <v>Maceyle Gabriela</v>
       </c>
-      <c r="D14" s="28" t="s">
-        <v>85</v>
-      </c>
-      <c r="E14" s="86">
-        <v>3157.7776559999998</v>
-      </c>
-      <c r="F14" s="86"/>
-      <c r="G14" s="107">
+      <c r="D14" s="26" t="s">
+        <v>81</v>
+      </c>
+      <c r="E14" s="76">
+        <v>7584.9209673599998</v>
+      </c>
+      <c r="F14" s="76">
+        <v>0</v>
+      </c>
+      <c r="G14" s="97">
         <f t="shared" si="0"/>
-        <v>3157.7776559999998</v>
-      </c>
-      <c r="H14" s="107">
+        <v>7584.9209673599998</v>
+      </c>
+      <c r="H14" s="97">
         <f t="shared" si="1"/>
-        <v>189.46665935999997</v>
-      </c>
-      <c r="I14" s="39">
+        <v>455.09525804159995</v>
+      </c>
+      <c r="I14" s="30">
         <v>1.32</v>
       </c>
-      <c r="J14" s="108">
+      <c r="J14" s="98">
         <f t="shared" si="2"/>
-        <v>4237.6766520000001</v>
-      </c>
-      <c r="K14" s="109"/>
-      <c r="L14" s="110">
+        <v>19659.724656000002</v>
+      </c>
+      <c r="K14" s="99">
         <f t="shared" si="3"/>
-        <v>7584.9209673599998</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="111" t="s">
+        <v>27699.740881401602</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="100" t="s">
         <v>9</v>
       </c>
-      <c r="B15" s="112"/>
-      <c r="C15" s="113"/>
-      <c r="D15" s="113"/>
-      <c r="E15" s="114">
+      <c r="B15" s="101"/>
+      <c r="C15" s="102"/>
+      <c r="D15" s="102"/>
+      <c r="E15" s="103">
         <f>SUM(E5:E14)</f>
-        <v>1053688.4995540974</v>
-      </c>
-      <c r="F15" s="115">
+        <v>1391322.6935273435</v>
+      </c>
+      <c r="F15" s="104">
         <f>SUM(F5:F14)</f>
-        <v>173513.09999999998</v>
-      </c>
-      <c r="G15" s="115"/>
-      <c r="H15" s="116">
+        <v>304433.89977409336</v>
+      </c>
+      <c r="G15" s="104"/>
+      <c r="H15" s="105">
         <f>SUM(H5:H14)</f>
-        <v>52810.523973245843</v>
-      </c>
-      <c r="I15" s="117">
+        <v>65213.327625194994</v>
+      </c>
+      <c r="I15" s="106">
         <f t="shared" ref="I15" si="4">SUM(I5:I14)</f>
         <v>100</v>
       </c>
-      <c r="J15" s="118">
+      <c r="J15" s="107">
         <f>SUM(J5:J14)</f>
-        <v>321036.11</v>
-      </c>
-      <c r="K15" s="114">
-        <f>SUM(K5:K11)</f>
-        <v>137300.66</v>
-      </c>
-      <c r="L15" s="114">
-        <f>SUM(L5:L14)</f>
-        <v>1391322.6935273435</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13" ht="217.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="127" t="s">
-        <v>86</v>
-      </c>
-      <c r="B16" s="127"/>
-      <c r="C16" s="127"/>
-      <c r="D16" s="127"/>
-      <c r="E16" s="127"/>
-      <c r="F16" s="127"/>
-      <c r="G16" s="127"/>
-      <c r="H16" s="127"/>
-      <c r="I16" s="127"/>
-      <c r="J16" s="127"/>
-      <c r="K16" s="127"/>
-      <c r="L16" s="127"/>
+        <v>1489373.08</v>
+      </c>
+      <c r="K15" s="103">
+        <f>SUM(K5:K14)</f>
+        <v>2641475.2013784451</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" ht="217.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="113" t="s">
+        <v>82</v>
+      </c>
+      <c r="B16" s="113"/>
+      <c r="C16" s="113"/>
+      <c r="D16" s="113"/>
+      <c r="E16" s="113"/>
+      <c r="F16" s="113"/>
+      <c r="G16" s="113"/>
+      <c r="H16" s="113"/>
+      <c r="I16" s="113"/>
+      <c r="J16" s="113"/>
+      <c r="K16" s="113"/>
     </row>
   </sheetData>
-  <mergeCells count="20">
-    <mergeCell ref="A14:B14"/>
+  <mergeCells count="19">
     <mergeCell ref="H1:I1"/>
-    <mergeCell ref="A16:L16"/>
+    <mergeCell ref="A16:K16"/>
     <mergeCell ref="I3:I4"/>
     <mergeCell ref="A6:B6"/>
     <mergeCell ref="A7:B7"/>
@@ -2540,11 +2545,11 @@
     <mergeCell ref="D3:D4"/>
     <mergeCell ref="A3:B4"/>
     <mergeCell ref="A5:B5"/>
-    <mergeCell ref="K3:K4"/>
     <mergeCell ref="J3:J4"/>
     <mergeCell ref="A11:B11"/>
     <mergeCell ref="A12:B12"/>
     <mergeCell ref="A13:B13"/>
+    <mergeCell ref="A14:B14"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -2555,521 +2560,521 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:M34"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="6" max="7" width="15.44140625" customWidth="1"/>
-    <col min="8" max="8" width="18.33203125" customWidth="1"/>
-    <col min="9" max="9" width="13.5546875" customWidth="1"/>
-    <col min="10" max="10" width="22.5546875" customWidth="1"/>
-    <col min="11" max="11" width="13.88671875" customWidth="1"/>
+    <col min="6" max="7" width="15.42578125" customWidth="1"/>
+    <col min="8" max="8" width="18.28515625" customWidth="1"/>
+    <col min="9" max="9" width="13.5703125" customWidth="1"/>
+    <col min="10" max="10" width="22.5703125" customWidth="1"/>
+    <col min="11" max="11" width="13.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="17.399999999999999" x14ac:dyDescent="0.4">
-      <c r="B1" s="49" t="s">
-        <v>48</v>
-      </c>
-      <c r="C1" s="50" t="s">
-        <v>80</v>
-      </c>
-      <c r="D1" s="51"/>
+    <row r="1" spans="1:13" ht="18" x14ac:dyDescent="0.35">
+      <c r="B1" s="39" t="s">
+        <v>45</v>
+      </c>
+      <c r="C1" s="40" t="s">
+        <v>77</v>
+      </c>
+      <c r="D1" s="41"/>
       <c r="F1" t="s">
         <v>24</v>
       </c>
       <c r="G1" t="s">
-        <v>50</v>
-      </c>
-      <c r="H1" s="80">
+        <v>47</v>
+      </c>
+      <c r="H1" s="70">
         <f>308832.09-171531.43</f>
         <v>137300.66000000003</v>
       </c>
-      <c r="K1" s="52"/>
-      <c r="L1" s="53"/>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="H2" s="54"/>
-      <c r="I2" s="54"/>
-      <c r="J2" s="54"/>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="B3" s="55" t="s">
+      <c r="K1" s="42"/>
+      <c r="L1" s="43"/>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="H2" s="44"/>
+      <c r="I2" s="44"/>
+      <c r="J2" s="44"/>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="B3" s="45" t="s">
+        <v>48</v>
+      </c>
+      <c r="C3" s="39" t="s">
+        <v>49</v>
+      </c>
+      <c r="D3" s="39" t="s">
+        <v>49</v>
+      </c>
+      <c r="E3" s="39" t="s">
+        <v>50</v>
+      </c>
+      <c r="F3" s="39" t="s">
         <v>51</v>
       </c>
-      <c r="C3" s="49" t="s">
+      <c r="G3" s="39" t="s">
         <v>52</v>
       </c>
-      <c r="D3" s="49" t="s">
-        <v>52</v>
-      </c>
-      <c r="E3" s="49" t="s">
+      <c r="H3" s="46" t="s">
         <v>53</v>
       </c>
-      <c r="F3" s="49" t="s">
+      <c r="I3" s="45"/>
+      <c r="J3" s="45"/>
+      <c r="K3" s="4"/>
+      <c r="M3" s="47"/>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="B4" s="45"/>
+      <c r="C4" s="39" t="s">
         <v>54</v>
       </c>
-      <c r="G3" s="49" t="s">
+      <c r="D4" s="39" t="s">
         <v>55</v>
       </c>
-      <c r="H3" s="56" t="s">
-        <v>56</v>
-      </c>
-      <c r="I3" s="55"/>
-      <c r="J3" s="55"/>
-      <c r="K3" s="4"/>
-      <c r="M3" s="57"/>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="B4" s="55"/>
-      <c r="C4" s="49" t="s">
-        <v>57</v>
-      </c>
-      <c r="D4" s="49" t="s">
-        <v>58</v>
-      </c>
-      <c r="E4" s="49"/>
-      <c r="F4" s="49"/>
-      <c r="H4" s="58">
+      <c r="E4" s="39"/>
+      <c r="F4" s="39"/>
+      <c r="H4" s="48">
         <f>H1</f>
         <v>137300.66000000003</v>
       </c>
-      <c r="I4" s="58"/>
-      <c r="J4" s="58"/>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="I4" s="48"/>
+      <c r="J4" s="48"/>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="B5" s="55">
+        <v>56</v>
+      </c>
+      <c r="B5" s="45">
         <v>1</v>
       </c>
       <c r="C5">
         <v>7817</v>
       </c>
-      <c r="D5" s="51">
+      <c r="D5" s="41">
         <f>C5+20</f>
         <v>7837</v>
       </c>
-      <c r="E5" s="55">
+      <c r="E5" s="45">
         <f>D5-C5</f>
         <v>20</v>
       </c>
-      <c r="F5" s="55">
+      <c r="F5" s="45">
         <f>E5*100/D14</f>
         <v>7.2727272727272725</v>
       </c>
       <c r="G5" s="4"/>
-      <c r="H5" s="59">
+      <c r="H5" s="49">
         <f>H4*(F5/100)</f>
         <v>9985.5025454545466</v>
       </c>
-      <c r="I5" s="55"/>
+      <c r="I5" s="45"/>
       <c r="J5" s="4"/>
       <c r="K5" s="4"/>
-      <c r="L5" s="60"/>
-      <c r="M5" s="61"/>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="L5" s="50"/>
+      <c r="M5" s="51"/>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="B6" s="55">
+        <v>57</v>
+      </c>
+      <c r="B6" s="45">
         <v>2</v>
       </c>
       <c r="C6">
         <v>7174</v>
       </c>
-      <c r="D6" s="51">
+      <c r="D6" s="41">
         <f>C6+98</f>
         <v>7272</v>
       </c>
-      <c r="E6" s="55">
+      <c r="E6" s="45">
         <f>D6-C6</f>
         <v>98</v>
       </c>
-      <c r="F6" s="55">
+      <c r="F6" s="45">
         <f>E6*100/D14</f>
         <v>35.636363636363633</v>
       </c>
       <c r="G6" s="4"/>
-      <c r="H6" s="59">
+      <c r="H6" s="49">
         <f>H4*(F6/100)</f>
         <v>48928.962472727282</v>
       </c>
-      <c r="I6" s="55"/>
+      <c r="I6" s="45"/>
       <c r="J6" s="4"/>
       <c r="K6" s="4"/>
-      <c r="L6" s="60"/>
-      <c r="M6" s="61"/>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="L6" s="50"/>
+      <c r="M6" s="51"/>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="B7" s="55">
+        <v>58</v>
+      </c>
+      <c r="B7" s="45">
         <v>3</v>
       </c>
       <c r="C7">
         <v>7791</v>
       </c>
-      <c r="D7" s="51">
+      <c r="D7" s="41">
         <f>C7+97</f>
         <v>7888</v>
       </c>
-      <c r="E7" s="55">
+      <c r="E7" s="45">
         <f t="shared" ref="E7:E11" si="0">D7-C7</f>
         <v>97</v>
       </c>
-      <c r="F7" s="55">
+      <c r="F7" s="45">
         <f>E7*100/D14</f>
         <v>35.272727272727273</v>
       </c>
-      <c r="H7" s="62">
+      <c r="H7" s="52">
         <f>H4*(F7/100)</f>
         <v>48429.687345454557</v>
       </c>
-      <c r="I7" s="49"/>
+      <c r="I7" s="39"/>
       <c r="J7" s="4"/>
       <c r="K7" s="4"/>
-      <c r="L7" s="60"/>
-      <c r="M7" s="61"/>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="L7" s="50"/>
+      <c r="M7" s="51"/>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="B8" s="55">
+        <v>59</v>
+      </c>
+      <c r="B8" s="45">
         <v>4</v>
       </c>
       <c r="C8">
         <v>9369</v>
       </c>
-      <c r="D8" s="51">
+      <c r="D8" s="41">
         <f>C8+20</f>
         <v>9389</v>
       </c>
-      <c r="E8" s="55">
+      <c r="E8" s="45">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="F8" s="55">
+      <c r="F8" s="45">
         <f>E8*100/D14</f>
         <v>7.2727272727272725</v>
       </c>
       <c r="G8" s="4"/>
-      <c r="H8" s="59">
+      <c r="H8" s="49">
         <f>H4*(F8/100)</f>
         <v>9985.5025454545466</v>
       </c>
-      <c r="I8" s="55"/>
+      <c r="I8" s="45"/>
       <c r="J8" s="4"/>
       <c r="K8" s="4"/>
-      <c r="L8" s="60"/>
-      <c r="M8" s="61"/>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="L8" s="50"/>
+      <c r="M8" s="51"/>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="B9" s="55">
+        <v>60</v>
+      </c>
+      <c r="B9" s="45">
         <v>5</v>
       </c>
       <c r="C9">
         <v>10695</v>
       </c>
-      <c r="D9" s="51">
+      <c r="D9" s="41">
         <f>C9</f>
         <v>10695</v>
       </c>
-      <c r="E9" s="55">
+      <c r="E9" s="45">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F9" s="55">
+      <c r="F9" s="45">
         <f>E9*100/D14</f>
         <v>0</v>
       </c>
       <c r="G9" s="4"/>
-      <c r="H9" s="59">
+      <c r="H9" s="49">
         <f>H4*(F9/100)</f>
         <v>0</v>
       </c>
-      <c r="I9" s="55"/>
+      <c r="I9" s="45"/>
       <c r="J9" s="4"/>
       <c r="K9" s="4"/>
-      <c r="L9" s="60"/>
-      <c r="M9" s="61"/>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="L9" s="50"/>
+      <c r="M9" s="51"/>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="B10" s="55">
+        <v>61</v>
+      </c>
+      <c r="B10" s="45">
         <v>6</v>
       </c>
       <c r="C10">
         <v>10767</v>
       </c>
-      <c r="D10" s="51">
+      <c r="D10" s="41">
         <f>C10+20</f>
         <v>10787</v>
       </c>
-      <c r="E10" s="55">
+      <c r="E10" s="45">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="F10" s="55">
+      <c r="F10" s="45">
         <f>E10*100/D14</f>
         <v>7.2727272727272725</v>
       </c>
       <c r="G10" s="4"/>
-      <c r="H10" s="59">
+      <c r="H10" s="49">
         <f>H4*(F10/100)</f>
         <v>9985.5025454545466</v>
       </c>
-      <c r="I10" s="55"/>
+      <c r="I10" s="45"/>
       <c r="J10" s="4"/>
       <c r="K10" s="4"/>
-      <c r="L10" s="60"/>
-      <c r="M10" s="61"/>
-    </row>
-    <row r="11" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="L10" s="50"/>
+      <c r="M10" s="51"/>
+    </row>
+    <row r="11" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="B11" s="55">
+        <v>62</v>
+      </c>
+      <c r="B11" s="45">
         <v>7</v>
       </c>
       <c r="C11">
         <v>13240</v>
       </c>
-      <c r="D11" s="51">
+      <c r="D11" s="41">
         <f>C11+20</f>
         <v>13260</v>
       </c>
-      <c r="E11" s="55">
+      <c r="E11" s="45">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="F11" s="55">
+      <c r="F11" s="45">
         <f>E11*100/D14</f>
         <v>7.2727272727272725</v>
       </c>
       <c r="G11" s="4"/>
-      <c r="H11" s="59">
+      <c r="H11" s="49">
         <f>H4*(F11/100)</f>
         <v>9985.5025454545466</v>
       </c>
-      <c r="I11" s="55"/>
+      <c r="I11" s="45"/>
       <c r="J11" s="4"/>
       <c r="K11" s="4"/>
-      <c r="L11" s="60"/>
-      <c r="M11" s="61"/>
-    </row>
-    <row r="12" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="63"/>
-      <c r="C12" s="64">
+      <c r="L11" s="50"/>
+      <c r="M11" s="51"/>
+    </row>
+    <row r="12" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B12" s="53"/>
+      <c r="C12" s="54">
         <f>SUM(C5:C11)</f>
         <v>66853</v>
       </c>
-      <c r="D12" s="64">
+      <c r="D12" s="54">
         <f>SUM(D5:D11)</f>
         <v>67128</v>
       </c>
-      <c r="E12" s="65">
+      <c r="E12" s="55">
         <f>SUM(E5:E11)</f>
         <v>275</v>
       </c>
-      <c r="F12" s="64">
+      <c r="F12" s="54">
         <f>SUM(F5:F11)</f>
         <v>99.999999999999986</v>
       </c>
-      <c r="G12" s="26"/>
-      <c r="H12" s="94">
+      <c r="G12" s="24"/>
+      <c r="H12" s="84">
         <f>SUM(H5:H11)</f>
         <v>137300.66</v>
       </c>
-      <c r="I12" s="63"/>
-      <c r="J12" s="63"/>
-      <c r="K12" s="63"/>
-      <c r="L12" s="66"/>
-    </row>
-    <row r="13" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C13" s="67"/>
-      <c r="H13" s="55"/>
-      <c r="I13" s="55"/>
-      <c r="J13" s="55"/>
-    </row>
-    <row r="14" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="I12" s="53"/>
+      <c r="J12" s="53"/>
+      <c r="K12" s="53"/>
+      <c r="L12" s="56"/>
+    </row>
+    <row r="13" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C13" s="57"/>
+      <c r="H13" s="45"/>
+      <c r="I13" s="45"/>
+      <c r="J13" s="45"/>
+    </row>
+    <row r="14" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B14" t="s">
-        <v>66</v>
-      </c>
-      <c r="D14" s="68">
+        <v>63</v>
+      </c>
+      <c r="D14" s="58">
         <f>D12-C12</f>
         <v>275</v>
       </c>
-      <c r="H14" s="55"/>
-      <c r="I14" s="55"/>
-      <c r="J14" s="55"/>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="H14" s="45"/>
+      <c r="I14" s="45"/>
+      <c r="J14" s="45"/>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
-        <v>67</v>
-      </c>
-      <c r="H15" s="55"/>
-      <c r="I15" s="55"/>
-      <c r="J15" s="55"/>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="B16" s="55"/>
-      <c r="C16" s="49"/>
-      <c r="D16" s="49"/>
-      <c r="E16" s="49"/>
-      <c r="F16" s="49"/>
-      <c r="H16" s="49"/>
-      <c r="I16" s="49"/>
-      <c r="J16" s="49"/>
+        <v>64</v>
+      </c>
+      <c r="H15" s="45"/>
+      <c r="I15" s="45"/>
+      <c r="J15" s="45"/>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="B16" s="45"/>
+      <c r="C16" s="39"/>
+      <c r="D16" s="39"/>
+      <c r="E16" s="39"/>
+      <c r="F16" s="39"/>
+      <c r="H16" s="39"/>
+      <c r="I16" s="39"/>
+      <c r="J16" s="39"/>
       <c r="K16" s="4"/>
     </row>
-    <row r="17" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="B17" s="55"/>
-      <c r="C17" s="49"/>
-      <c r="D17" s="49"/>
-      <c r="E17" s="49"/>
-      <c r="F17" s="49"/>
-      <c r="H17" s="58"/>
-      <c r="I17" s="58"/>
-      <c r="J17" s="58"/>
-    </row>
-    <row r="18" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="H18" s="55"/>
-      <c r="I18" s="55"/>
-      <c r="J18" s="55"/>
-    </row>
-    <row r="19" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="C19" s="69"/>
-      <c r="D19" s="70"/>
-      <c r="E19" s="70"/>
-      <c r="F19" s="70"/>
-      <c r="G19" s="70"/>
-      <c r="H19" s="71"/>
-      <c r="I19" s="71"/>
-      <c r="J19" s="71"/>
-      <c r="K19" s="70"/>
-      <c r="L19" s="70"/>
-      <c r="M19" s="72"/>
-    </row>
-    <row r="20" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="C20" s="73"/>
+    <row r="17" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B17" s="45"/>
+      <c r="C17" s="39"/>
+      <c r="D17" s="39"/>
+      <c r="E17" s="39"/>
+      <c r="F17" s="39"/>
+      <c r="H17" s="48"/>
+      <c r="I17" s="48"/>
+      <c r="J17" s="48"/>
+    </row>
+    <row r="18" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H18" s="45"/>
+      <c r="I18" s="45"/>
+      <c r="J18" s="45"/>
+    </row>
+    <row r="19" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="C19" s="59"/>
+      <c r="D19" s="60"/>
+      <c r="E19" s="60"/>
+      <c r="F19" s="60"/>
+      <c r="G19" s="60"/>
+      <c r="H19" s="61"/>
+      <c r="I19" s="61"/>
+      <c r="J19" s="61"/>
+      <c r="K19" s="60"/>
+      <c r="L19" s="60"/>
+      <c r="M19" s="62"/>
+    </row>
+    <row r="20" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="C20" s="63"/>
       <c r="E20" t="s">
-        <v>68</v>
-      </c>
-      <c r="H20" s="74">
+        <v>65</v>
+      </c>
+      <c r="H20" s="64">
         <f>D14</f>
         <v>275</v>
       </c>
-      <c r="I20" s="74"/>
-      <c r="J20" s="74"/>
+      <c r="I20" s="64"/>
+      <c r="J20" s="64"/>
       <c r="K20" t="s">
-        <v>69</v>
-      </c>
-      <c r="M20" s="75"/>
-    </row>
-    <row r="21" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="C21" s="73"/>
+        <v>66</v>
+      </c>
+      <c r="M20" s="65"/>
+    </row>
+    <row r="21" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="C21" s="63"/>
       <c r="D21" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="E21">
         <v>7</v>
       </c>
       <c r="F21" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="G21">
         <v>197</v>
       </c>
       <c r="H21" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="K21" t="s">
-        <v>73</v>
-      </c>
-      <c r="M21" s="75"/>
-    </row>
-    <row r="22" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C22" s="76"/>
-      <c r="D22" s="77"/>
-      <c r="E22" s="77"/>
-      <c r="F22" s="77"/>
-      <c r="G22" s="77"/>
-      <c r="H22" s="77"/>
-      <c r="I22" s="77"/>
-      <c r="J22" s="77"/>
-      <c r="K22" s="77"/>
-      <c r="L22" s="77"/>
-      <c r="M22" s="78"/>
-    </row>
-    <row r="25" spans="2:13" x14ac:dyDescent="0.3">
-      <c r="K25" s="79" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="26" spans="2:13" x14ac:dyDescent="0.3">
+        <v>70</v>
+      </c>
+      <c r="M21" s="65"/>
+    </row>
+    <row r="22" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C22" s="66"/>
+      <c r="D22" s="67"/>
+      <c r="E22" s="67"/>
+      <c r="F22" s="67"/>
+      <c r="G22" s="67"/>
+      <c r="H22" s="67"/>
+      <c r="I22" s="67"/>
+      <c r="J22" s="67"/>
+      <c r="K22" s="67"/>
+      <c r="L22" s="67"/>
+      <c r="M22" s="68"/>
+    </row>
+    <row r="25" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="K25" s="69" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="26" spans="2:13" x14ac:dyDescent="0.25">
       <c r="G26" s="4"/>
-      <c r="K26" s="57"/>
-    </row>
-    <row r="27" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="K26" s="47"/>
+    </row>
+    <row r="27" spans="2:13" x14ac:dyDescent="0.25">
       <c r="I27" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="J27" t="s">
         <v>4</v>
       </c>
       <c r="K27" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="28" spans="2:13" x14ac:dyDescent="0.3">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="28" spans="2:13" x14ac:dyDescent="0.25">
       <c r="G28" s="4"/>
       <c r="H28" s="4" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="I28" s="4">
         <v>29829</v>
       </c>
-      <c r="J28" s="60">
+      <c r="J28" s="50">
         <v>16000</v>
       </c>
-      <c r="K28" s="61">
+      <c r="K28" s="51">
         <f t="shared" ref="K28" si="1">I28+J28</f>
         <v>45829</v>
       </c>
     </row>
-    <row r="31" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:13" x14ac:dyDescent="0.25">
       <c r="J31" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="K31">
         <v>117067</v>
       </c>
     </row>
-    <row r="32" spans="2:13" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:13" x14ac:dyDescent="0.25">
       <c r="J32" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="K32">
         <v>-55000</v>
       </c>
     </row>
-    <row r="33" spans="10:11" x14ac:dyDescent="0.3">
-      <c r="J33" s="57" t="s">
-        <v>78</v>
+    <row r="33" spans="10:11" x14ac:dyDescent="0.25">
+      <c r="J33" s="47" t="s">
+        <v>75</v>
       </c>
       <c r="K33">
         <v>43965</v>
       </c>
     </row>
-    <row r="34" spans="10:11" x14ac:dyDescent="0.3">
-      <c r="K34" s="51">
+    <row r="34" spans="10:11" x14ac:dyDescent="0.25">
+      <c r="K34" s="41">
         <f>SUM(K31:K33)</f>
         <v>106032</v>
       </c>
